--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104746</v>
       </c>
       <c r="B2" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104772</v>
       </c>
       <c r="B3" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104747</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104746</v>
       </c>
       <c r="B2" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104772</v>
       </c>
       <c r="B3" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104747</v>
       </c>
       <c r="B4" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104746</v>
       </c>
       <c r="B2" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104772</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104747</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,220 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132867729</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97359</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>633266</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6660997</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132867730</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97359</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633258</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6661009</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>132867729</v>
       </c>
       <c r="B5" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132867730</v>
       </c>
       <c r="B6" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>132867729</v>
       </c>
       <c r="B5" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>132867730</v>
       </c>
       <c r="B6" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 58546-2025 artfynd.xlsx
+++ b/artfynd/A 58546-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130104746</v>
+        <v>130104744</v>
       </c>
       <c r="B2" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633246</v>
+        <v>633208</v>
       </c>
       <c r="R2" t="n">
-        <v>6661031</v>
+        <v>6661035</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -735,7 +735,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104772</v>
+        <v>130104746</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633193</v>
+        <v>633246</v>
       </c>
       <c r="R3" t="n">
-        <v>6661012</v>
+        <v>6661031</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,7 +872,7 @@
         <v>130104747</v>
       </c>
       <c r="B4" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132867729</v>
+        <v>130104754</v>
       </c>
       <c r="B5" t="n">
-        <v>97372</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633266</v>
+        <v>633178</v>
       </c>
       <c r="R5" t="n">
-        <v>6660997</v>
+        <v>6661028</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1026,27 +1026,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132867730</v>
+        <v>130104755</v>
       </c>
       <c r="B6" t="n">
-        <v>97372</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,17 +1094,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633258</v>
+        <v>633175</v>
       </c>
       <c r="R6" t="n">
-        <v>6661009</v>
+        <v>6661029</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1133,27 +1123,17 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Skuttunge</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1177,6 +1157,836 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132867729</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97435</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633266</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6660997</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132867730</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97435</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>633258</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6661009</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132867731</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97435</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>53</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633211</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6661035</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130104767</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>633161</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6660959</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130104783</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>633213</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6661055</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>19 25 buketter</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132867726</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633219</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6661053</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130104770</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>633197</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6661030</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130104772</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>633193</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6661012</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
